--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11080,6 +11080,66 @@
         <v>306.73</v>
       </c>
       <c r="H355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="C356" t="n">
+        <v>318.02</v>
+      </c>
+      <c r="D356" t="n">
+        <v>324.49</v>
+      </c>
+      <c r="E356" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="F356" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="G356" t="n">
+        <v>303.48</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="C357" t="n">
+        <v>318.54</v>
+      </c>
+      <c r="D357" t="n">
+        <v>325.28</v>
+      </c>
+      <c r="E357" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="F357" t="n">
+        <v>314.33</v>
+      </c>
+      <c r="G357" t="n">
+        <v>303.48</v>
+      </c>
+      <c r="H357" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11096,7 +11156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15459,6 +15519,26 @@
       </c>
       <c r="B436" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -15627,28 +15707,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04637330517872019</v>
+        <v>0.03932140447976781</v>
       </c>
       <c r="J2" t="n">
+        <v>356</v>
+      </c>
+      <c r="K2" t="n">
         <v>354</v>
       </c>
-      <c r="K2" t="n">
-        <v>352</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.003472657371326848</v>
+        <v>0.002512285766872124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.552167655146129</v>
+        <v>4.559631313401177</v>
       </c>
       <c r="N2" t="n">
-        <v>32.83149108440918</v>
+        <v>32.86769071736769</v>
       </c>
       <c r="O2" t="n">
-        <v>5.729877056657427</v>
+        <v>5.733035035421264</v>
       </c>
       <c r="P2" t="n">
-        <v>328.2000491832674</v>
+        <v>328.2799053436544</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15705,28 +15785,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04349472161540729</v>
+        <v>0.03712886249813303</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002007142720677368</v>
+        <v>0.001475739830373746</v>
       </c>
       <c r="M3" t="n">
-        <v>5.71529027086441</v>
+        <v>5.713129420721391</v>
       </c>
       <c r="N3" t="n">
-        <v>49.80649798256276</v>
+        <v>49.70575017771719</v>
       </c>
       <c r="O3" t="n">
-        <v>7.057371889206546</v>
+        <v>7.050230505289681</v>
       </c>
       <c r="P3" t="n">
-        <v>322.7994277741296</v>
+        <v>322.8716099847966</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15783,28 +15863,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08498642058261867</v>
+        <v>0.08251628690503214</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008505767891706872</v>
+        <v>0.008113554119558164</v>
       </c>
       <c r="M4" t="n">
-        <v>5.397935079388657</v>
+        <v>5.379481639663323</v>
       </c>
       <c r="N4" t="n">
-        <v>44.57993781094305</v>
+        <v>44.35725835567204</v>
       </c>
       <c r="O4" t="n">
-        <v>6.676820935965188</v>
+        <v>6.660124500012897</v>
       </c>
       <c r="P4" t="n">
-        <v>324.8003874760822</v>
+        <v>324.8283945348045</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15861,28 +15941,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04272289880167958</v>
+        <v>-0.0482453114907102</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001897257126962981</v>
+        <v>0.002440824098120076</v>
       </c>
       <c r="M5" t="n">
-        <v>5.777013231571013</v>
+        <v>5.768548169200947</v>
       </c>
       <c r="N5" t="n">
-        <v>50.84335471438526</v>
+        <v>50.69287673382179</v>
       </c>
       <c r="O5" t="n">
-        <v>7.13045263040049</v>
+        <v>7.119893028256941</v>
       </c>
       <c r="P5" t="n">
-        <v>329.5880411088458</v>
+        <v>329.6506588028924</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15939,28 +16019,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05629220144537682</v>
+        <v>-0.06667056942573356</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002696357097029867</v>
+        <v>0.003794493931665421</v>
       </c>
       <c r="M6" t="n">
-        <v>6.343914652087456</v>
+        <v>6.359063240767583</v>
       </c>
       <c r="N6" t="n">
-        <v>62.05977269688636</v>
+        <v>62.18675947991581</v>
       </c>
       <c r="O6" t="n">
-        <v>7.877802529696106</v>
+        <v>7.885858195524175</v>
       </c>
       <c r="P6" t="n">
-        <v>324.7715778559795</v>
+        <v>324.8892581308789</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16017,28 +16097,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4229674881853617</v>
+        <v>0.411431999136808</v>
       </c>
       <c r="J7" t="n">
+        <v>356</v>
+      </c>
+      <c r="K7" t="n">
         <v>354</v>
       </c>
-      <c r="K7" t="n">
-        <v>352</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05882317105478996</v>
+        <v>0.05626320030972931</v>
       </c>
       <c r="M7" t="n">
-        <v>9.304178050968467</v>
+        <v>9.316855434028517</v>
       </c>
       <c r="N7" t="n">
-        <v>152.0096849256552</v>
+        <v>151.740633600224</v>
       </c>
       <c r="O7" t="n">
-        <v>12.3292207752824</v>
+        <v>12.31830481844901</v>
       </c>
       <c r="P7" t="n">
-        <v>302.3812651819555</v>
+        <v>302.512066021612</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16080,7 +16160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30977,6 +31057,90 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-35.1183737068011,173.96329670771271</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-35.11874390815829,173.96407487219764</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-35.119029673312745,173.96492326489167</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-35.119335830417356,173.96580459434338</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-35.11955727249269,173.96678694194176</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-35.11958031317616,173.9677624569345</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-35.11836733463311,173.96330058172015</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-35.118739713810186,173.9640774221626</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-35.119023179539326,173.96492682727714</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-35.11932975166272,173.96580666105555</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-35.119550874131285,173.96678719144379</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-35.11958031317616,173.9677624569345</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,6 +11142,96 @@
       <c r="H357" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>323.06</v>
+      </c>
+      <c r="C358" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="D358" t="n">
+        <v>325.39</v>
+      </c>
+      <c r="E358" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="F358" t="n">
+        <v>315.14</v>
+      </c>
+      <c r="G358" t="n">
+        <v>303.67</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="C359" t="n">
+        <v>319.24</v>
+      </c>
+      <c r="D359" t="n">
+        <v>325.87</v>
+      </c>
+      <c r="E359" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="F359" t="n">
+        <v>316.09</v>
+      </c>
+      <c r="G359" t="n">
+        <v>304.33</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="C360" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D360" t="n">
+        <v>325.51</v>
+      </c>
+      <c r="E360" t="n">
+        <v>324.24</v>
+      </c>
+      <c r="F360" t="n">
+        <v>315.34</v>
+      </c>
+      <c r="G360" t="n">
+        <v>304.33</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15539,6 +15629,36 @@
       </c>
       <c r="B438" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -15707,28 +15827,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03932140447976781</v>
+        <v>0.02957286182914743</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002512285766872124</v>
+        <v>0.001435152332767142</v>
       </c>
       <c r="M2" t="n">
-        <v>4.559631313401177</v>
+        <v>4.567489432862851</v>
       </c>
       <c r="N2" t="n">
-        <v>32.86769071736769</v>
+        <v>32.88043948103716</v>
       </c>
       <c r="O2" t="n">
-        <v>5.733035035421264</v>
+        <v>5.734146796258112</v>
       </c>
       <c r="P2" t="n">
-        <v>328.2799053436544</v>
+        <v>328.3905518034359</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15785,28 +15905,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03712886249813303</v>
+        <v>0.02910522151436861</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001475739830373746</v>
+        <v>0.0009199061737361625</v>
       </c>
       <c r="M3" t="n">
-        <v>5.713129420721391</v>
+        <v>5.702624602340579</v>
       </c>
       <c r="N3" t="n">
-        <v>49.70575017771719</v>
+        <v>49.48468713222862</v>
       </c>
       <c r="O3" t="n">
-        <v>7.050230505289681</v>
+        <v>7.034535317434167</v>
       </c>
       <c r="P3" t="n">
-        <v>322.8716099847966</v>
+        <v>322.9627992161222</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15863,28 +15983,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08251628690503214</v>
+        <v>0.08010761786623695</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008113554119558164</v>
+        <v>0.007782702123788066</v>
       </c>
       <c r="M4" t="n">
-        <v>5.379481639663323</v>
+        <v>5.345945978441931</v>
       </c>
       <c r="N4" t="n">
-        <v>44.35725835567204</v>
+        <v>44.00441571669088</v>
       </c>
       <c r="O4" t="n">
-        <v>6.660124500012897</v>
+        <v>6.633582419529501</v>
       </c>
       <c r="P4" t="n">
-        <v>324.8283945348045</v>
+        <v>324.8557682993981</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15941,28 +16061,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0482453114907102</v>
+        <v>-0.05501464792503619</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002440824098120076</v>
+        <v>0.003219084475775902</v>
       </c>
       <c r="M5" t="n">
-        <v>5.768548169200947</v>
+        <v>5.749436547620675</v>
       </c>
       <c r="N5" t="n">
-        <v>50.69287673382179</v>
+        <v>50.4076272381644</v>
       </c>
       <c r="O5" t="n">
-        <v>7.119893028256941</v>
+        <v>7.099832902129767</v>
       </c>
       <c r="P5" t="n">
-        <v>329.6506588028924</v>
+        <v>329.727590772372</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16019,28 +16139,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06667056942573356</v>
+        <v>-0.07910559346109221</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003794493931665421</v>
+        <v>0.00538774879893944</v>
       </c>
       <c r="M6" t="n">
-        <v>6.359063240767583</v>
+        <v>6.366559085413377</v>
       </c>
       <c r="N6" t="n">
-        <v>62.18675947991581</v>
+        <v>62.13454037264136</v>
       </c>
       <c r="O6" t="n">
-        <v>7.885858195524175</v>
+        <v>7.882546566474654</v>
       </c>
       <c r="P6" t="n">
-        <v>324.8892581308789</v>
+        <v>325.0305805539593</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16097,28 +16217,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.411431999136808</v>
+        <v>0.3957788515112303</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05626320030972931</v>
+        <v>0.0529169921858148</v>
       </c>
       <c r="M7" t="n">
-        <v>9.316855434028517</v>
+        <v>9.327533103494046</v>
       </c>
       <c r="N7" t="n">
-        <v>151.740633600224</v>
+        <v>151.2086285017112</v>
       </c>
       <c r="O7" t="n">
-        <v>12.31830481844901</v>
+        <v>12.29669177062315</v>
       </c>
       <c r="P7" t="n">
-        <v>302.512066021612</v>
+        <v>302.6899598406183</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16160,7 +16280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31141,6 +31261,132 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-35.11837120633013,173.96329822789292</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-35.118736487388546,173.96407938367398</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-35.11902227534302,173.96492732330546</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-35.11932836223308,173.96580713344687</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-35.11954357459221,173.9667874760869</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-35.11957860812992,173.96776225480014</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-35.118367011991694,173.96330077787243</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-35.118734067572284,173.96408085480738</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-35.11901832975909,173.9649294877925</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-35.11932471498027,173.965808373474</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-35.11953501340438,173.96678780992752</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-35.11957268533774,173.9677615526492</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-35.118367011991694,173.96330077787243</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-35.11873761663613,173.964078697145</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-35.11902128894704,173.9649278644272</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-35.11932636492797,173.96580781250933</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-35.11954177223688,173.96678754636912</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-35.11957268533774,173.9677615526492</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
